--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2556,32 +2556,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135268145</v>
+        <v>135474571</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2589,23 +2589,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459555</v>
+        <v>459609</v>
       </c>
       <c r="R19" t="n">
-        <v>6697284</v>
+        <v>6697146</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,27 +2629,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sandbad, Färsk spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,44 +2654,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135268434</v>
+        <v>135474759</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2709,23 +2699,23 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459468</v>
+        <v>459547</v>
       </c>
       <c r="R20" t="n">
-        <v>6697063</v>
+        <v>6697032</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2749,27 +2739,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Sandbad</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,72 +2764,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135267991</v>
+        <v>135268145</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459597</v>
+        <v>459555</v>
       </c>
       <c r="R21" t="n">
-        <v>6697065</v>
+        <v>6697284</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2876,90 +2852,100 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sandbad, Färsk spillning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135268144</v>
+        <v>135268434</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459378</v>
+        <v>459468</v>
       </c>
       <c r="R22" t="n">
-        <v>6697193</v>
+        <v>6697063</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2986,76 +2972,86 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135268158</v>
+        <v>135474496</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3063,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459418</v>
+        <v>459556</v>
       </c>
       <c r="R23" t="n">
-        <v>6697172</v>
+        <v>6697250</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3093,12 +3089,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Även nyligen använt sandbad</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,7 +3108,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135268167</v>
+        <v>135267991</v>
       </c>
       <c r="B24" t="n">
         <v>99195</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459438</v>
+        <v>459597</v>
       </c>
       <c r="R24" t="n">
-        <v>6697163</v>
+        <v>6697065</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3236,7 +3236,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135269033</v>
+        <v>135268144</v>
       </c>
       <c r="B25" t="n">
         <v>99195</v>
@@ -3266,26 +3266,30 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459572</v>
+        <v>459378</v>
       </c>
       <c r="R25" t="n">
-        <v>6697038</v>
+        <v>6697193</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3312,24 +3316,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>7 st m blomstjälk</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,19 +3334,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135269106</v>
+        <v>135268158</v>
       </c>
       <c r="B26" t="n">
         <v>99195</v>
@@ -3387,7 +3376,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3400,17 +3389,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459597</v>
+        <v>459418</v>
       </c>
       <c r="R26" t="n">
-        <v>6697015</v>
+        <v>6697172</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3437,19 +3426,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,19 +3444,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135269668</v>
+        <v>135268167</v>
       </c>
       <c r="B27" t="n">
         <v>99195</v>
@@ -3507,7 +3486,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3520,17 +3499,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459530</v>
+        <v>459438</v>
       </c>
       <c r="R27" t="n">
-        <v>6697191</v>
+        <v>6697163</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3557,19 +3536,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,19 +3554,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135269679</v>
+        <v>135269033</v>
       </c>
       <c r="B28" t="n">
         <v>99195</v>
@@ -3627,14 +3596,10 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3644,10 +3609,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459519</v>
+        <v>459572</v>
       </c>
       <c r="R28" t="n">
-        <v>6697199</v>
+        <v>6697038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3690,6 +3655,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>7 st m blomstjälk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,7 +3687,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135269745</v>
+        <v>135269106</v>
       </c>
       <c r="B29" t="n">
         <v>99195</v>
@@ -3747,7 +3717,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3764,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459550</v>
+        <v>459597</v>
       </c>
       <c r="R29" t="n">
-        <v>6697217</v>
+        <v>6697015</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,11 +3782,6 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>8st m blomsterstjälk</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3839,6 +3804,701 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135269668</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>459530</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697191</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135269679</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>459519</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697199</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135269745</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>459550</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697217</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>8st m blomsterstjälk</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135474512</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>459498</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697230</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135474643</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>459584</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6697158</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135474708</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>459618</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6697086</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135267996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135267998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268027</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268131</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268152</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268175</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268177</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268182</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268187</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268176</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268318</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269009</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,6 +2388,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269076</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269545</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2553,6 +2638,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269595</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474571</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2773,6 +2868,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474759</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2893,6 +2993,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268145</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268434</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3233,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474496</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3233,6 +3348,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135267991</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3343,6 +3463,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268144</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3453,6 +3578,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268158</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3563,6 +3693,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268167</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3684,6 +3819,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3804,6 +3944,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269106</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3924,6 +4069,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269668</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4044,6 +4194,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269679</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4169,6 +4324,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269745</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4279,6 +4439,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474512</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4389,6 +4554,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474643</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4499,8 +4669,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135268003</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135267996</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135267998</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>135268017</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135268027</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135268131</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>135268152</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>135268175</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>135268177</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>135268182</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135268187</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,56 +1896,51 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135268176</v>
+        <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459551</v>
+        <v>459623</v>
       </c>
       <c r="R13" t="n">
-        <v>6697254</v>
+        <v>6697006</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,27 +1964,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack, gamla</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,79 +1983,75 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268176</t>
+          <t>https://artportalen.se/Sighting/135663069</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135268318</v>
+        <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459452</v>
+        <v>459631</v>
       </c>
       <c r="R14" t="n">
-        <v>6697152</v>
+        <v>6697062</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,27 +2075,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack Två träd</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,79 +2094,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268318</t>
+          <t>https://artportalen.se/Sighting/135663083</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135269009</v>
+        <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459547</v>
+        <v>459618</v>
       </c>
       <c r="R15" t="n">
-        <v>6697069</v>
+        <v>6697075</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,27 +2186,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,79 +2205,75 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269009</t>
+          <t>https://artportalen.se/Sighting/135663096</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135269076</v>
+        <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459580</v>
+        <v>459616</v>
       </c>
       <c r="R16" t="n">
-        <v>6697022</v>
+        <v>6697161</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,27 +2297,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,79 +2316,75 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269076</t>
+          <t>https://artportalen.se/Sighting/135663140</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135269545</v>
+        <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459589</v>
+        <v>459592</v>
       </c>
       <c r="R17" t="n">
-        <v>6697062</v>
+        <v>6697192</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,27 +2408,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,33 +2427,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269545</t>
+          <t>https://artportalen.se/Sighting/135663159</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135269595</v>
+        <v>135268176</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,7 +2484,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2564,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459580</v>
+        <v>459551</v>
       </c>
       <c r="R18" t="n">
-        <v>6697114</v>
+        <v>6697254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2529,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2539,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack, gamla</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,16 +2570,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269595</t>
+          <t>https://artportalen.se/Sighting/135268176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135474571</v>
+        <v>135268318</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,23 +2609,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459609</v>
+        <v>459452</v>
       </c>
       <c r="R19" t="n">
-        <v>6697146</v>
+        <v>6697152</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2719,17 +2649,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack Två träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,27 +2684,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474571</t>
+          <t>https://artportalen.se/Sighting/135268318</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135474759</v>
+        <v>135269009</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2800,17 +2740,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
         <v>459547</v>
       </c>
       <c r="R20" t="n">
-        <v>6697032</v>
+        <v>6697069</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,17 +2774,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,49 +2809,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474759</t>
+          <t>https://artportalen.se/Sighting/135269009</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135268145</v>
+        <v>135269076</v>
       </c>
       <c r="B21" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2909,7 +2859,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2919,10 +2869,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459555</v>
+        <v>459580</v>
       </c>
       <c r="R21" t="n">
-        <v>6697284</v>
+        <v>6697022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2904,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,12 +2914,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Sandbad, Färsk spillning</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,38 +2945,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268145</t>
+          <t>https://artportalen.se/Sighting/135269076</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135268434</v>
+        <v>135269545</v>
       </c>
       <c r="B22" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3034,7 +2984,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3044,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459468</v>
+        <v>459589</v>
       </c>
       <c r="R22" t="n">
-        <v>6697063</v>
+        <v>6697062</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,7 +3044,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Sandbad</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,38 +3070,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268434</t>
+          <t>https://artportalen.se/Sighting/135269545</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135474496</v>
+        <v>135269595</v>
       </c>
       <c r="B23" t="n">
-        <v>57162</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3159,23 +3109,23 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459556</v>
+        <v>459580</v>
       </c>
       <c r="R23" t="n">
-        <v>6697250</v>
+        <v>6697114</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,17 +3149,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Även nyligen använt sandbad</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,63 +3184,59 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474496</t>
+          <t>https://artportalen.se/Sighting/135269595</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135267991</v>
+        <v>135474571</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3288,10 +3244,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459597</v>
+        <v>459609</v>
       </c>
       <c r="R24" t="n">
-        <v>6697065</v>
+        <v>6697146</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3318,12 +3274,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,7 +3293,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3350,52 +3310,48 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135267991</t>
+          <t>https://artportalen.se/Sighting/135474571</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135268144</v>
+        <v>135474759</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3403,10 +3359,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459378</v>
+        <v>459547</v>
       </c>
       <c r="R25" t="n">
-        <v>6697193</v>
+        <v>6697032</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3433,12 +3389,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,7 +3408,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3465,66 +3425,62 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268144</t>
+          <t>https://artportalen.se/Sighting/135474759</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135268158</v>
+        <v>135268145</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>57167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459418</v>
+        <v>459555</v>
       </c>
       <c r="R26" t="n">
-        <v>6697172</v>
+        <v>6697284</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3551,95 +3507,105 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sandbad, Färsk spillning</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268158</t>
+          <t>https://artportalen.se/Sighting/135268145</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135268167</v>
+        <v>135268434</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>57167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459438</v>
+        <v>459468</v>
       </c>
       <c r="R27" t="n">
-        <v>6697163</v>
+        <v>6697063</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3666,91 +3632,105 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268167</t>
+          <t>https://artportalen.se/Sighting/135268434</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135269033</v>
+        <v>135474496</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>57167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459572</v>
+        <v>459556</v>
       </c>
       <c r="R28" t="n">
-        <v>6697038</v>
+        <v>6697250</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3774,27 +3754,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>7 st m blomstjälk</t>
+          <t>Även nyligen använt sandbad</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,34 +3773,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269033</t>
+          <t>https://artportalen.se/Sighting/135474496</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135269106</v>
+        <v>135267991</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3857,7 +3826,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3870,17 +3839,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>459597</v>
       </c>
       <c r="R29" t="n">
-        <v>6697015</v>
+        <v>6697065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3907,19 +3876,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3935,27 +3894,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269106</t>
+          <t>https://artportalen.se/Sighting/135267991</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135269668</v>
+        <v>135268144</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3982,7 +3941,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3995,17 +3954,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459530</v>
+        <v>459378</v>
       </c>
       <c r="R30" t="n">
-        <v>6697191</v>
+        <v>6697193</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4032,19 +3991,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4060,27 +4009,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269668</t>
+          <t>https://artportalen.se/Sighting/135268144</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135269679</v>
+        <v>135268158</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4056,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4120,17 +4069,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459519</v>
+        <v>459418</v>
       </c>
       <c r="R31" t="n">
-        <v>6697199</v>
+        <v>6697172</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4157,19 +4106,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4185,27 +4124,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269679</t>
+          <t>https://artportalen.se/Sighting/135268158</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135269745</v>
+        <v>135268167</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4232,7 +4171,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4245,17 +4184,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Butjärnberget, Dlr</t>
+          <t>Butjärnsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459550</v>
+        <v>459438</v>
       </c>
       <c r="R32" t="n">
-        <v>6697217</v>
+        <v>6697163</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4282,24 +4221,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>8st m blomsterstjälk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4315,27 +4239,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135269745</t>
+          <t>https://artportalen.se/Sighting/135268167</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135474512</v>
+        <v>135269033</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4362,30 +4286,26 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459498</v>
+        <v>459572</v>
       </c>
       <c r="R33" t="n">
-        <v>6697230</v>
+        <v>6697038</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4409,12 +4329,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>7 st m blomstjälk</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4430,27 +4365,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474512</t>
+          <t>https://artportalen.se/Sighting/135269033</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135474643</v>
+        <v>135269106</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4477,7 +4412,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4490,17 +4425,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459584</v>
+        <v>459597</v>
       </c>
       <c r="R34" t="n">
-        <v>6697158</v>
+        <v>6697015</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4524,12 +4459,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4545,27 +4490,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135474643</t>
+          <t>https://artportalen.se/Sighting/135269106</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135474708</v>
+        <v>135269668</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4592,7 +4537,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4605,17 +4550,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Butjärnsberget, Dlr</t>
+          <t>Butjärnberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459618</v>
+        <v>459530</v>
       </c>
       <c r="R35" t="n">
-        <v>6697086</v>
+        <v>6697191</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4639,12 +4584,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4660,16 +4615,616 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269668</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135269679</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>459519</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6697199</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269679</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135269745</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Butjärnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>459550</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6697217</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>8st m blomsterstjälk</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135269745</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135474512</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>459498</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6697230</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474512</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135474643</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>459584</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6697158</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135474643</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135474708</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Butjärnsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>459618</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6697086</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135474708</t>
         </is>
@@ -4711,6 +5266,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135268003</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135267996</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135267998</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>135268017</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>135268027</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135268131</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>135268152</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>135268175</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>135268177</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>135268182</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>135268187</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135267991</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>135268144</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>135268158</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>135268167</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>135269033</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>135269106</v>
       </c>
       <c r="B34" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>135269668</v>
       </c>
       <c r="B35" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>135269679</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135269745</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135474512</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135474643</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>135474708</v>
       </c>
       <c r="B40" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135268003</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135267991</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>135268144</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>135268158</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>135268167</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>135269033</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>135269106</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>135269668</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>135269679</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135269745</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135474512</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135474643</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>135474708</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>135474571</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>135474759</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135474496</v>
       </c>
       <c r="B28" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>135474512</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>135474643</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>135474708</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3363-2026 artfynd.xlsx
+++ b/artfynd/A 3363-2026 artfynd.xlsx
@@ -1899,7 +1899,7 @@
         <v>135663069</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>135663083</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135663096</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>135663140</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>135663159</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
